--- a/Website/static/downloads/showcase/excel/report-workflow.xlsx
+++ b/Website/static/downloads/showcase/excel/report-workflow.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:bookViews>
+    <x:workbookView/>
+  </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" r:id="R538834cffde745bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" r:id="R959e59272b1e44c6"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="R2b79563c32b546ab"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="R14ff64cf36e84e43"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="16">
   <x:si>
     <x:t>{{ReportTitle}}</x:t>
   </x:si>
   <x:si>
+    <x:t>Revenue, cost and margin by region and product line. Margin columns are formulas.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Region</x:t>
   </x:si>
   <x:si>
+    <x:t>Product</x:t>
+  </x:si>
+  <x:si>
     <x:t>Revenue</x:t>
   </x:si>
   <x:si>
@@ -28,28 +37,90 @@
     <x:t>Margin</x:t>
   </x:si>
   <x:si>
+    <x:t>Margin %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>North</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Platform</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Services</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Support</x:t>
+  </x:si>
+  <x:si>
+    <x:t>South</x:t>
+  </x:si>
+  <x:si>
     <x:t>East</x:t>
   </x:si>
   <x:si>
     <x:t>West</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="164" formatCode="#,##0"/>
+    <x:numFmt numFmtId="165" formatCode="0.0%"/>
+  </x:numFmts>
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="20"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF5B6B7F"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+        <x:bgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF7"/>
+        <x:bgColor rgb="FFE8EEF7"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -58,8 +129,22 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <x:xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <x:xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -84,7 +169,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue and Margin</a:t>
+              <a:t>Revenue and margin by region</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -103,7 +188,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Report'!$B$2</c:f>
+              <c:f>'Report'!$I$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -115,20 +200,26 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Report'!$A$3:$A$4</c:f>
+              <c:f>'Report'!$H$5:$H$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Report'!$B$3:$B$4</c:f>
+              <c:f>'Report'!$I$5:$I$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -139,43 +230,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Report'!$C$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Cost</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Report'!$A$3:$A$4</c:f>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Report'!$C$3:$C$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Report'!$D$2</c:f>
+              <c:f>'Report'!$J$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -187,20 +242,26 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Report'!$A$3:$A$4</c:f>
+              <c:f>'Report'!$H$5:$H$8</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Report'!$D$3:$D$4</c:f>
+              <c:f>'Report'!$J$5:$J$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>70</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -270,12 +331,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4000500" cy="2286000"/>
+    <xdr:ext cx="3333750" cy="2238375"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="1" name="Chart 1"/>
@@ -285,11 +346,11 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
-        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="4000500" cy="2286000"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="3333750" cy="2238375"/>
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8d530e277644bd4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra3439c7c015e43c5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -300,32 +361,44 @@
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
 <x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="RevenuePivot" cacheId="1" applyNumberFormats="1" applyBorderFormats="1" applyPatternFormats="1" applyAlignmentFormats="1" applyWidthHeightFormats="1" dataCaption="Values" pivotTableStyle="PivotStyleMedium9" preserveFormatting="1" useAutoFormatting="1" rowGrandTotals="1" colGrandTotals="1" outlineData="0" compactData="1" multipleFieldFilters="1">
-  <x:location ref="F2:G3" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <x:pivotFields count="4">
-    <x:pivotField axis="axisRow" showAll="1"/>
-    <x:pivotField dataField="1" showAll="1"/>
-    <x:pivotField showAll="1"/>
-    <x:pivotField showAll="1"/>
+  <x:location ref="A20:B21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <x:pivotFields count="6">
+    <x:pivotField axis="axisRow" showAll="0">
+      <x:items count="5">
+        <x:item x="0"/>
+        <x:item x="1"/>
+        <x:item x="2"/>
+        <x:item x="3"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField showAll="0"/>
+    <x:pivotField dataField="1" showAll="0"/>
+    <x:pivotField showAll="0"/>
+    <x:pivotField showAll="0"/>
+    <x:pivotField showAll="0"/>
   </x:pivotFields>
   <x:rowFields count="1">
     <x:field x="0"/>
   </x:rowFields>
   <x:dataFields count="1">
-    <x:dataField name="Total Revenue" fld="1" subtotal="sum"/>
+    <x:dataField name="Total Revenue" fld="2" subtotal="sum"/>
   </x:dataFields>
 </x:pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RevenueData" displayName="RevenueData" ref="A2:D4" headerRowCount="1" totalsRowShown="0">
-  <x:autoFilter ref="A2:D4"/>
-  <x:tableColumns count="4">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RevenueData" displayName="RevenueData" ref="A4:F16" headerRowCount="1" totalsRowShown="0">
+  <x:autoFilter ref="A4:F16"/>
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="Region"/>
-    <x:tableColumn id="2" name="Revenue"/>
-    <x:tableColumn id="3" name="Cost"/>
-    <x:tableColumn id="4" name="Margin"/>
+    <x:tableColumn id="2" name="Product"/>
+    <x:tableColumn id="3" name="Revenue"/>
+    <x:tableColumn id="4" name="Cost"/>
+    <x:tableColumn id="5" name="Margin"/>
+    <x:tableColumn id="6" name="Margin %"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -614,61 +687,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:J17"/>
+  <x:sheetFormatPr xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="3" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <x:is xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <x:t>Executive revenue report</x:t>
-        </x:is>
-      </c>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Regional revenue report</t>
+        </is>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" t="n">
-        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">B3-C3</x:f>
-        <v>70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
-        <v>90</v>
-      </c>
-      <c r="C4" t="n">
-        <v>40</v>
-      </c>
-      <c r="D4" t="n">
-        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">B4-C4</x:f>
-        <v>50</v>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>482000</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>301000</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C5-D5</x:f>
+        <v>181000</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E5/C5</x:f>
+        <v>0.3755186721991701</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H5,$C$5:$C$16)</x:f>
+        <v>836000</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H5,$E$5:$E$16)</x:f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>236000</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>171000</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C6-D6</x:f>
+        <v>65000</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E6/C6</x:f>
+        <v>0.2754237288135593</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H6,$C$5:$C$16)</x:f>
+        <v>692000</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H6,$E$5:$E$16)</x:f>
+        <v>214000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>64000</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C7-D7</x:f>
+        <v>54000</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E7/C7</x:f>
+        <v>0.4576271186440678</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H7,$C$5:$C$16)</x:f>
+        <v>968000</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H7,$E$5:$E$16)</x:f>
+        <v>372000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>391000</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>262000</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C8-D8</x:f>
+        <v>129000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E8/C8</x:f>
+        <v>0.329923273657289</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H8,$C$5:$C$16)</x:f>
+        <v>843000</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUMIF($A$5:$A$16,H8,$E$5:$E$16)</x:f>
+        <v>288000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>204000</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>158000</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C9-D9</x:f>
+        <v>46000</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E9/C9</x:f>
+        <v>0.22549019607843138</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>97000</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C10-D10</x:f>
+        <v>39000</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E10/C10</x:f>
+        <v>0.4020618556701031</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>538000</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>322000</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C11-D11</x:f>
+        <v>216000</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E11/C11</x:f>
+        <v>0.40148698884758366</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>289000</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>201000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C12-D12</x:f>
+        <v>88000</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E12/C12</x:f>
+        <v>0.3044982698961938</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>141000</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C13-D13</x:f>
+        <v>68000</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E13/C13</x:f>
+        <v>0.48226950354609927</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>455000</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>296000</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C14-D14</x:f>
+        <v>159000</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E14/C14</x:f>
+        <v>0.34945054945054943</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>262000</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>189000</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C15-D15</x:f>
+        <v>73000</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E15/C15</x:f>
+        <v>0.2786259541984733</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>126000</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">C16-D16</x:f>
+        <v>56000</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E16/C16</x:f>
+        <v>0.4444444444444444</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="12" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUM(C5:C16)</x:f>
+        <v>3339000</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUM(D5:D16)</x:f>
+        <v>2165000</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">SUM(E5:E16)</x:f>
+        <v>1174000</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <x:f xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ca="0">E17/C17</x:f>
+        <v>0.35160227613057804</v>
       </c>
     </row>
   </sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R221505681ff449ca"/>
+  <x:mergeCells xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2">
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" sqref="F5:F16">
+    <x:cfRule type="colorScale" priority="1">
+      <x:colorScale>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="F8D7DA"/>
+        <x:color rgb="C9ECD3"/>
+      </x:colorScale>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R2d035d49a1fd412c"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -676,25 +1101,33 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" saveData="0" refreshOnLoad="1" recordCount="2">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R52a97d7810a643b3" saveData="0" refreshOnLoad="1" recordCount="12">
   <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A2:D4" sheet="Report"/>
+    <x:worksheetSource ref="A4:F16" sheet="Report"/>
   </x:cacheSource>
-  <x:cacheFields count="4">
+  <x:cacheFields count="6">
     <x:cacheField name="Region">
-      <x:sharedItems containsDate="0" containsString="1" containsBlank="0" containsNumber="0" count="2">
+      <x:sharedItems containsSemiMixedTypes="1" containsNonDate="1" containsDate="0" containsString="1" containsBlank="0" containsMixedTypes="0" containsNumber="0" count="4">
+        <x:s v="North"/>
+        <x:s v="South"/>
         <x:s v="East"/>
         <x:s v="West"/>
       </x:sharedItems>
     </x:cacheField>
+    <x:cacheField name="Product">
+      <x:sharedItems containsSemiMixedTypes="0" containsNonDate="1" containsDate="0" containsString="0" containsBlank="0" containsMixedTypes="0" containsNumber="0"/>
+    </x:cacheField>
     <x:cacheField name="Revenue">
-      <x:sharedItems containsDate="0" containsString="0" containsBlank="0" containsNumber="0"/>
+      <x:sharedItems containsSemiMixedTypes="0" containsNonDate="1" containsDate="0" containsString="0" containsBlank="0" containsMixedTypes="0" containsNumber="0"/>
     </x:cacheField>
     <x:cacheField name="Cost">
-      <x:sharedItems containsDate="0" containsString="0" containsBlank="0" containsNumber="0"/>
+      <x:sharedItems containsSemiMixedTypes="0" containsNonDate="1" containsDate="0" containsString="0" containsBlank="0" containsMixedTypes="0" containsNumber="0"/>
     </x:cacheField>
     <x:cacheField name="Margin">
-      <x:sharedItems containsDate="0" containsString="0" containsBlank="0" containsNumber="0"/>
+      <x:sharedItems containsSemiMixedTypes="0" containsNonDate="1" containsDate="0" containsString="0" containsBlank="0" containsMixedTypes="0" containsNumber="0"/>
+    </x:cacheField>
+    <x:cacheField name="Margin %">
+      <x:sharedItems containsSemiMixedTypes="0" containsNonDate="1" containsDate="0" containsString="0" containsBlank="0" containsMixedTypes="0" containsNumber="0"/>
     </x:cacheField>
   </x:cacheFields>
 </x:pivotCacheDefinition>
